--- a/Docs/Report Docs/Плата управления БРВН BOM_v1.0.xlsx
+++ b/Docs/Report Docs/Плата управления БРВН BOM_v1.0.xlsx
@@ -699,7 +699,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H70"/>
+  <dimension ref="A1:H69"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -1689,7 +1689,7 @@
     <row r="33" ht="20" customHeight="1">
       <c r="A33" s="15" t="inlineStr">
         <is>
-          <t>J34, J35</t>
+          <t>J6, J16, J17, J34, J35</t>
         </is>
       </c>
       <c r="B33" s="13" t="inlineStr">
@@ -1714,14 +1714,14 @@
         </is>
       </c>
       <c r="G33" s="13" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="H33" s="14" t="inlineStr"/>
     </row>
     <row r="34" ht="20" customHeight="1">
       <c r="A34" s="15" t="inlineStr">
         <is>
-          <t>J6, J16, J17</t>
+          <t>J1</t>
         </is>
       </c>
       <c r="B34" s="13" t="inlineStr">
@@ -1731,13 +1731,17 @@
       </c>
       <c r="C34" s="13" t="inlineStr">
         <is>
-          <t>DS1073-01-2x2MR3T6</t>
-        </is>
-      </c>
-      <c r="D34" s="13" t="inlineStr"/>
+          <t>KLS1-207-1-04-S</t>
+        </is>
+      </c>
+      <c r="D34" s="13" t="inlineStr">
+        <is>
+          <t>DS-1021-1x4</t>
+        </is>
+      </c>
       <c r="E34" s="13" t="inlineStr">
         <is>
-          <t>Molex Mini-Fit Jr 5566-04A 2x02 P4.20mm</t>
+          <t>PinHeader 1x04 P2.54mm</t>
         </is>
       </c>
       <c r="F34" s="13" t="inlineStr">
@@ -1746,50 +1750,46 @@
         </is>
       </c>
       <c r="G34" s="13" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H34" s="14" t="inlineStr"/>
     </row>
     <row r="35" ht="20" customHeight="1">
-      <c r="A35" s="15" t="inlineStr">
-        <is>
-          <t>J1</t>
-        </is>
-      </c>
-      <c r="B35" s="13" t="inlineStr">
-        <is>
-          <t>~</t>
-        </is>
-      </c>
-      <c r="C35" s="13" t="inlineStr">
-        <is>
-          <t>KLS1-207-1-04-S</t>
-        </is>
-      </c>
-      <c r="D35" s="13" t="inlineStr">
-        <is>
-          <t>DS-1021-1x4</t>
-        </is>
-      </c>
-      <c r="E35" s="13" t="inlineStr">
-        <is>
-          <t>PinHeader 1x04 P2.54mm</t>
-        </is>
-      </c>
-      <c r="F35" s="13" t="inlineStr">
-        <is>
-          <t>Connector</t>
-        </is>
-      </c>
-      <c r="G35" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="H35" s="14" t="inlineStr"/>
+      <c r="A35" s="16" t="inlineStr">
+        <is>
+          <t>L4, L6</t>
+        </is>
+      </c>
+      <c r="B35" s="17" t="inlineStr">
+        <is>
+          <t>4.7u</t>
+        </is>
+      </c>
+      <c r="C35" s="17" t="inlineStr">
+        <is>
+          <t>LQH44PN4R7MP0L</t>
+        </is>
+      </c>
+      <c r="D35" s="17" t="inlineStr"/>
+      <c r="E35" s="17" t="inlineStr">
+        <is>
+          <t>SMD 1210</t>
+        </is>
+      </c>
+      <c r="F35" s="17" t="inlineStr">
+        <is>
+          <t>Inductor SMD</t>
+        </is>
+      </c>
+      <c r="G35" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="H35" s="18" t="inlineStr"/>
     </row>
     <row r="36" ht="20" customHeight="1">
       <c r="A36" s="16" t="inlineStr">
         <is>
-          <t>L4, L6</t>
+          <t>L2</t>
         </is>
       </c>
       <c r="B36" s="17" t="inlineStr">
@@ -1799,13 +1799,13 @@
       </c>
       <c r="C36" s="17" t="inlineStr">
         <is>
-          <t>LQH44PN4R7MP0L</t>
+          <t>NLC453232T-4R7K-PF</t>
         </is>
       </c>
       <c r="D36" s="17" t="inlineStr"/>
       <c r="E36" s="17" t="inlineStr">
         <is>
-          <t>SMD 1210</t>
+          <t>SMD 1812</t>
         </is>
       </c>
       <c r="F36" s="17" t="inlineStr">
@@ -1814,94 +1814,94 @@
         </is>
       </c>
       <c r="G36" s="17" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H36" s="18" t="inlineStr"/>
     </row>
     <row r="37" ht="20" customHeight="1">
       <c r="A37" s="16" t="inlineStr">
         <is>
-          <t>L2</t>
+          <t>L5, L7</t>
         </is>
       </c>
       <c r="B37" s="17" t="inlineStr">
         <is>
-          <t>4.7u</t>
+          <t>470u</t>
         </is>
       </c>
       <c r="C37" s="17" t="inlineStr">
         <is>
-          <t>NLC453232T-4R7K-PF</t>
+          <t>B82790C0474N215</t>
         </is>
       </c>
       <c r="D37" s="17" t="inlineStr"/>
       <c r="E37" s="17" t="inlineStr">
         <is>
-          <t>SMD 1812</t>
+          <t>B82790S0513N201</t>
         </is>
       </c>
       <c r="F37" s="17" t="inlineStr">
         <is>
-          <t>Inductor SMD</t>
+          <t>Inductor common mode SMD</t>
         </is>
       </c>
       <c r="G37" s="17" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H37" s="18" t="inlineStr"/>
     </row>
     <row r="38" ht="20" customHeight="1">
       <c r="A38" s="16" t="inlineStr">
         <is>
-          <t>L5, L7</t>
+          <t>L3</t>
         </is>
       </c>
       <c r="B38" s="17" t="inlineStr">
         <is>
-          <t>470u</t>
+          <t>6.8u</t>
         </is>
       </c>
       <c r="C38" s="17" t="inlineStr">
         <is>
-          <t>B82790C0474N215</t>
+          <t>LQH32CN6R8M53L</t>
         </is>
       </c>
       <c r="D38" s="17" t="inlineStr"/>
       <c r="E38" s="17" t="inlineStr">
         <is>
-          <t>B82790S0513N201</t>
+          <t>SMD 1210</t>
         </is>
       </c>
       <c r="F38" s="17" t="inlineStr">
         <is>
-          <t>Inductor common mode SMD</t>
+          <t>Inductor SMD</t>
         </is>
       </c>
       <c r="G38" s="17" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H38" s="18" t="inlineStr"/>
     </row>
     <row r="39" ht="20" customHeight="1">
       <c r="A39" s="16" t="inlineStr">
         <is>
-          <t>L3</t>
+          <t>L1</t>
         </is>
       </c>
       <c r="B39" s="17" t="inlineStr">
         <is>
-          <t>6.8u</t>
+          <t>~</t>
         </is>
       </c>
       <c r="C39" s="17" t="inlineStr">
         <is>
-          <t>LQH32CN6R8M53L</t>
+          <t>ACM2520-301-2P-T002</t>
         </is>
       </c>
       <c r="D39" s="17" t="inlineStr"/>
       <c r="E39" s="17" t="inlineStr">
         <is>
-          <t>SMD 1210</t>
+          <t>CommonModeChoke TDK ACM2520-2P</t>
         </is>
       </c>
       <c r="F39" s="17" t="inlineStr">
@@ -1915,41 +1915,41 @@
       <c r="H39" s="18" t="inlineStr"/>
     </row>
     <row r="40" ht="20" customHeight="1">
-      <c r="A40" s="16" t="inlineStr">
-        <is>
-          <t>L1</t>
-        </is>
-      </c>
-      <c r="B40" s="17" t="inlineStr">
+      <c r="A40" s="19" t="inlineStr">
+        <is>
+          <t>Q2, Q3, Q4, Q5</t>
+        </is>
+      </c>
+      <c r="B40" s="20" t="inlineStr">
         <is>
           <t>~</t>
         </is>
       </c>
-      <c r="C40" s="17" t="inlineStr">
-        <is>
-          <t>ACM2520-301-2P-T002</t>
-        </is>
-      </c>
-      <c r="D40" s="17" t="inlineStr"/>
-      <c r="E40" s="17" t="inlineStr">
-        <is>
-          <t>CommonModeChoke TDK ACM2520-2P</t>
-        </is>
-      </c>
-      <c r="F40" s="17" t="inlineStr">
-        <is>
-          <t>Inductor SMD</t>
-        </is>
-      </c>
-      <c r="G40" s="17" t="n">
-        <v>1</v>
-      </c>
-      <c r="H40" s="18" t="inlineStr"/>
+      <c r="C40" s="20" t="inlineStr">
+        <is>
+          <t>BSP75N</t>
+        </is>
+      </c>
+      <c r="D40" s="20" t="inlineStr"/>
+      <c r="E40" s="20" t="inlineStr">
+        <is>
+          <t>SOT-223</t>
+        </is>
+      </c>
+      <c r="F40" s="20" t="inlineStr">
+        <is>
+          <t>Self-Protected Low Side Driver with Temperature and Current Limit, SOT−223</t>
+        </is>
+      </c>
+      <c r="G40" s="20" t="n">
+        <v>4</v>
+      </c>
+      <c r="H40" s="21" t="inlineStr"/>
     </row>
     <row r="41" ht="20" customHeight="1">
       <c r="A41" s="19" t="inlineStr">
         <is>
-          <t>Q2, Q3, Q4, Q5</t>
+          <t>Q7, Q8</t>
         </is>
       </c>
       <c r="B41" s="20" t="inlineStr">
@@ -1959,29 +1959,29 @@
       </c>
       <c r="C41" s="20" t="inlineStr">
         <is>
-          <t>BSP75N</t>
+          <t>BC847</t>
         </is>
       </c>
       <c r="D41" s="20" t="inlineStr"/>
       <c r="E41" s="20" t="inlineStr">
         <is>
-          <t>SOT-223</t>
+          <t>SOT-23</t>
         </is>
       </c>
       <c r="F41" s="20" t="inlineStr">
         <is>
-          <t>Self-Protected Low Side Driver with Temperature and Current Limit, SOT−223</t>
+          <t>Bipolar N</t>
         </is>
       </c>
       <c r="G41" s="20" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H41" s="21" t="inlineStr"/>
     </row>
     <row r="42" ht="20" customHeight="1">
       <c r="A42" s="19" t="inlineStr">
         <is>
-          <t>Q7, Q8</t>
+          <t>Q9, Q10</t>
         </is>
       </c>
       <c r="B42" s="20" t="inlineStr">
@@ -1991,7 +1991,7 @@
       </c>
       <c r="C42" s="20" t="inlineStr">
         <is>
-          <t>BC847</t>
+          <t>BC857</t>
         </is>
       </c>
       <c r="D42" s="20" t="inlineStr"/>
@@ -2002,7 +2002,7 @@
       </c>
       <c r="F42" s="20" t="inlineStr">
         <is>
-          <t>Bipolar N</t>
+          <t>Bipolar P</t>
         </is>
       </c>
       <c r="G42" s="20" t="n">
@@ -2013,7 +2013,7 @@
     <row r="43" ht="20" customHeight="1">
       <c r="A43" s="19" t="inlineStr">
         <is>
-          <t>Q9, Q10</t>
+          <t>Q1, Q6</t>
         </is>
       </c>
       <c r="B43" s="20" t="inlineStr">
@@ -2023,18 +2023,18 @@
       </c>
       <c r="C43" s="20" t="inlineStr">
         <is>
-          <t>BC857</t>
+          <t>20N06</t>
         </is>
       </c>
       <c r="D43" s="20" t="inlineStr"/>
       <c r="E43" s="20" t="inlineStr">
         <is>
-          <t>SOT-23</t>
+          <t>TO-252-2</t>
         </is>
       </c>
       <c r="F43" s="20" t="inlineStr">
         <is>
-          <t>Bipolar P</t>
+          <t>N_channel MOSFET</t>
         </is>
       </c>
       <c r="G43" s="20" t="n">
@@ -2043,46 +2043,42 @@
       <c r="H43" s="21" t="inlineStr"/>
     </row>
     <row r="44" ht="20" customHeight="1">
-      <c r="A44" s="19" t="inlineStr">
-        <is>
-          <t>Q1, Q6</t>
-        </is>
-      </c>
-      <c r="B44" s="20" t="inlineStr">
-        <is>
-          <t>~</t>
-        </is>
-      </c>
-      <c r="C44" s="20" t="inlineStr">
-        <is>
-          <t>20N06</t>
-        </is>
-      </c>
-      <c r="D44" s="20" t="inlineStr"/>
-      <c r="E44" s="20" t="inlineStr">
-        <is>
-          <t>TO-252-2</t>
-        </is>
-      </c>
-      <c r="F44" s="20" t="inlineStr">
-        <is>
-          <t>N_channel MOSFET</t>
-        </is>
-      </c>
-      <c r="G44" s="20" t="n">
-        <v>2</v>
-      </c>
-      <c r="H44" s="21" t="inlineStr"/>
+      <c r="A44" s="22" t="inlineStr">
+        <is>
+          <t>R57</t>
+        </is>
+      </c>
+      <c r="B44" s="23" t="inlineStr">
+        <is>
+          <t>1.1k</t>
+        </is>
+      </c>
+      <c r="C44" s="23" t="inlineStr"/>
+      <c r="D44" s="23" t="inlineStr"/>
+      <c r="E44" s="23" t="inlineStr">
+        <is>
+          <t>SMD 0805</t>
+        </is>
+      </c>
+      <c r="F44" s="23" t="inlineStr">
+        <is>
+          <t>Resistor SMD</t>
+        </is>
+      </c>
+      <c r="G44" s="23" t="n">
+        <v>1</v>
+      </c>
+      <c r="H44" s="24" t="inlineStr"/>
     </row>
     <row r="45" ht="20" customHeight="1">
       <c r="A45" s="22" t="inlineStr">
         <is>
-          <t>R57</t>
+          <t>R55</t>
         </is>
       </c>
       <c r="B45" s="23" t="inlineStr">
         <is>
-          <t>1.1k</t>
+          <t>100k</t>
         </is>
       </c>
       <c r="C45" s="23" t="inlineStr"/>
@@ -2103,14 +2099,14 @@
       <c r="H45" s="24" t="inlineStr"/>
     </row>
     <row r="46" ht="20" customHeight="1">
-      <c r="A46" s="22" t="inlineStr">
-        <is>
-          <t>R55</t>
+      <c r="A46" s="25" t="inlineStr">
+        <is>
+          <t>R11, R14, R24, R62, R65, R68, R71, R74, R77, R80, R83, R88, R89, R90, R91</t>
         </is>
       </c>
       <c r="B46" s="23" t="inlineStr">
         <is>
-          <t>100k</t>
+          <t>10k</t>
         </is>
       </c>
       <c r="C46" s="23" t="inlineStr"/>
@@ -2126,19 +2122,19 @@
         </is>
       </c>
       <c r="G46" s="23" t="n">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="H46" s="24" t="inlineStr"/>
     </row>
     <row r="47" ht="20" customHeight="1">
-      <c r="A47" s="25" t="inlineStr">
-        <is>
-          <t>R11, R14, R24, R62, R65, R68, R71, R74, R77, R80, R83, R88, R89, R90, R91</t>
+      <c r="A47" s="22" t="inlineStr">
+        <is>
+          <t>R7, R42, R135</t>
         </is>
       </c>
       <c r="B47" s="23" t="inlineStr">
         <is>
-          <t>10k</t>
+          <t>120</t>
         </is>
       </c>
       <c r="C47" s="23" t="inlineStr"/>
@@ -2154,26 +2150,26 @@
         </is>
       </c>
       <c r="G47" s="23" t="n">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="H47" s="24" t="inlineStr"/>
     </row>
     <row r="48" ht="20" customHeight="1">
       <c r="A48" s="22" t="inlineStr">
         <is>
-          <t>R7, R42, R135</t>
+          <t>R56, R87</t>
         </is>
       </c>
       <c r="B48" s="23" t="inlineStr">
         <is>
-          <t>120</t>
+          <t>14.3</t>
         </is>
       </c>
       <c r="C48" s="23" t="inlineStr"/>
       <c r="D48" s="23" t="inlineStr"/>
       <c r="E48" s="23" t="inlineStr">
         <is>
-          <t>SMD 0805</t>
+          <t>SMD 2512</t>
         </is>
       </c>
       <c r="F48" s="23" t="inlineStr">
@@ -2182,19 +2178,19 @@
         </is>
       </c>
       <c r="G48" s="23" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H48" s="24" t="inlineStr"/>
     </row>
     <row r="49" ht="20" customHeight="1">
-      <c r="A49" s="22" t="inlineStr">
-        <is>
-          <t>R56, R87</t>
+      <c r="A49" s="25" t="inlineStr">
+        <is>
+          <t>R25, R26, R27, R28, R31, R34, R48, R51, R132</t>
         </is>
       </c>
       <c r="B49" s="23" t="inlineStr">
         <is>
-          <t>14.3</t>
+          <t>150k</t>
         </is>
       </c>
       <c r="C49" s="23" t="inlineStr"/>
@@ -2210,26 +2206,26 @@
         </is>
       </c>
       <c r="G49" s="23" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="H49" s="24" t="inlineStr"/>
     </row>
     <row r="50" ht="20" customHeight="1">
       <c r="A50" s="25" t="inlineStr">
         <is>
-          <t>R25, R26, R27, R28, R31, R34, R48, R51, R132</t>
+          <t>R4, R8, R12, R13, R18, R21, R33, R43, R46, R47, R59, R86, R92, R136, R139, R140</t>
         </is>
       </c>
       <c r="B50" s="23" t="inlineStr">
         <is>
-          <t>150k</t>
+          <t>1k</t>
         </is>
       </c>
       <c r="C50" s="23" t="inlineStr"/>
       <c r="D50" s="23" t="inlineStr"/>
       <c r="E50" s="23" t="inlineStr">
         <is>
-          <t>SMD 2512</t>
+          <t>SMD 0805</t>
         </is>
       </c>
       <c r="F50" s="23" t="inlineStr">
@@ -2238,19 +2234,19 @@
         </is>
       </c>
       <c r="G50" s="23" t="n">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="H50" s="24" t="inlineStr"/>
     </row>
     <row r="51" ht="20" customHeight="1">
-      <c r="A51" s="25" t="inlineStr">
-        <is>
-          <t>R4, R8, R12, R13, R18, R21, R33, R43, R46, R47, R59, R86, R92, R136, R139, R140</t>
+      <c r="A51" s="22" t="inlineStr">
+        <is>
+          <t>R54, R95</t>
         </is>
       </c>
       <c r="B51" s="23" t="inlineStr">
         <is>
-          <t>1k</t>
+          <t>20</t>
         </is>
       </c>
       <c r="C51" s="23" t="inlineStr"/>
@@ -2266,19 +2262,19 @@
         </is>
       </c>
       <c r="G51" s="23" t="n">
-        <v>16</v>
+        <v>2</v>
       </c>
       <c r="H51" s="24" t="inlineStr"/>
     </row>
     <row r="52" ht="20" customHeight="1">
       <c r="A52" s="22" t="inlineStr">
         <is>
-          <t>R54, R95</t>
+          <t>R23</t>
         </is>
       </c>
       <c r="B52" s="23" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>23.2k</t>
         </is>
       </c>
       <c r="C52" s="23" t="inlineStr"/>
@@ -2294,26 +2290,26 @@
         </is>
       </c>
       <c r="G52" s="23" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H52" s="24" t="inlineStr"/>
     </row>
     <row r="53" ht="20" customHeight="1">
-      <c r="A53" s="22" t="inlineStr">
-        <is>
-          <t>R23</t>
+      <c r="A53" s="25" t="inlineStr">
+        <is>
+          <t>R1, R2, R3, R6, R29, R30, R32, R41, R49, R50, R53, R134</t>
         </is>
       </c>
       <c r="B53" s="23" t="inlineStr">
         <is>
-          <t>23.2k</t>
+          <t>2M</t>
         </is>
       </c>
       <c r="C53" s="23" t="inlineStr"/>
       <c r="D53" s="23" t="inlineStr"/>
       <c r="E53" s="23" t="inlineStr">
         <is>
-          <t>SMD 0805</t>
+          <t>SMD 1206</t>
         </is>
       </c>
       <c r="F53" s="23" t="inlineStr">
@@ -2322,26 +2318,26 @@
         </is>
       </c>
       <c r="G53" s="23" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="H53" s="24" t="inlineStr"/>
     </row>
     <row r="54" ht="20" customHeight="1">
-      <c r="A54" s="25" t="inlineStr">
-        <is>
-          <t>R1, R2, R3, R6, R29, R30, R32, R41, R49, R50, R53, R134</t>
+      <c r="A54" s="22" t="inlineStr">
+        <is>
+          <t>R63, R69, R75, R81</t>
         </is>
       </c>
       <c r="B54" s="23" t="inlineStr">
         <is>
-          <t>2M</t>
+          <t>3.3k</t>
         </is>
       </c>
       <c r="C54" s="23" t="inlineStr"/>
       <c r="D54" s="23" t="inlineStr"/>
       <c r="E54" s="23" t="inlineStr">
         <is>
-          <t>SMD 1206</t>
+          <t>SMD 0805</t>
         </is>
       </c>
       <c r="F54" s="23" t="inlineStr">
@@ -2350,19 +2346,19 @@
         </is>
       </c>
       <c r="G54" s="23" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="H54" s="24" t="inlineStr"/>
     </row>
     <row r="55" ht="20" customHeight="1">
       <c r="A55" s="22" t="inlineStr">
         <is>
-          <t>R63, R69, R75, R81</t>
+          <t>R60, R66, R72, R78</t>
         </is>
       </c>
       <c r="B55" s="23" t="inlineStr">
         <is>
-          <t>3.3k</t>
+          <t>330</t>
         </is>
       </c>
       <c r="C55" s="23" t="inlineStr"/>
@@ -2385,12 +2381,12 @@
     <row r="56" ht="20" customHeight="1">
       <c r="A56" s="22" t="inlineStr">
         <is>
-          <t>R60, R66, R72, R78</t>
+          <t>R85</t>
         </is>
       </c>
       <c r="B56" s="23" t="inlineStr">
         <is>
-          <t>330</t>
+          <t>4.7k</t>
         </is>
       </c>
       <c r="C56" s="23" t="inlineStr"/>
@@ -2406,19 +2402,19 @@
         </is>
       </c>
       <c r="G56" s="23" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H56" s="24" t="inlineStr"/>
     </row>
     <row r="57" ht="20" customHeight="1">
       <c r="A57" s="22" t="inlineStr">
         <is>
-          <t>R85</t>
+          <t>R84</t>
         </is>
       </c>
       <c r="B57" s="23" t="inlineStr">
         <is>
-          <t>4.7k</t>
+          <t>470k</t>
         </is>
       </c>
       <c r="C57" s="23" t="inlineStr"/>
@@ -2441,12 +2437,12 @@
     <row r="58" ht="20" customHeight="1">
       <c r="A58" s="22" t="inlineStr">
         <is>
-          <t>R84</t>
+          <t>R10, R45, R138</t>
         </is>
       </c>
       <c r="B58" s="23" t="inlineStr">
         <is>
-          <t>470k</t>
+          <t>49.9</t>
         </is>
       </c>
       <c r="C58" s="23" t="inlineStr"/>
@@ -2462,19 +2458,19 @@
         </is>
       </c>
       <c r="G58" s="23" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H58" s="24" t="inlineStr"/>
     </row>
     <row r="59" ht="20" customHeight="1">
       <c r="A59" s="22" t="inlineStr">
         <is>
-          <t>R10, R45, R138</t>
+          <t>R37, R40</t>
         </is>
       </c>
       <c r="B59" s="23" t="inlineStr">
         <is>
-          <t>49.9</t>
+          <t>59</t>
         </is>
       </c>
       <c r="C59" s="23" t="inlineStr"/>
@@ -2490,19 +2486,19 @@
         </is>
       </c>
       <c r="G59" s="23" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H59" s="24" t="inlineStr"/>
     </row>
     <row r="60" ht="20" customHeight="1">
       <c r="A60" s="22" t="inlineStr">
         <is>
-          <t>R37, R40</t>
+          <t>R39, R52</t>
         </is>
       </c>
       <c r="B60" s="23" t="inlineStr">
         <is>
-          <t>59</t>
+          <t>750</t>
         </is>
       </c>
       <c r="C60" s="23" t="inlineStr"/>
@@ -2523,14 +2519,14 @@
       <c r="H60" s="24" t="inlineStr"/>
     </row>
     <row r="61" ht="20" customHeight="1">
-      <c r="A61" s="22" t="inlineStr">
-        <is>
-          <t>R39, R52</t>
+      <c r="A61" s="25" t="inlineStr">
+        <is>
+          <t>R61, R64, R67, R70, R73, R76, R79, R82</t>
         </is>
       </c>
       <c r="B61" s="23" t="inlineStr">
         <is>
-          <t>750</t>
+          <t>8.2k</t>
         </is>
       </c>
       <c r="C61" s="23" t="inlineStr"/>
@@ -2546,26 +2542,26 @@
         </is>
       </c>
       <c r="G61" s="23" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="H61" s="24" t="inlineStr"/>
     </row>
     <row r="62" ht="20" customHeight="1">
       <c r="A62" s="25" t="inlineStr">
         <is>
-          <t>R61, R64, R67, R70, R73, R76, R79, R82</t>
+          <t>R5, R9, R38, R44, R133, R137</t>
         </is>
       </c>
       <c r="B62" s="23" t="inlineStr">
         <is>
-          <t>8.2k</t>
+          <t>8k</t>
         </is>
       </c>
       <c r="C62" s="23" t="inlineStr"/>
       <c r="D62" s="23" t="inlineStr"/>
       <c r="E62" s="23" t="inlineStr">
         <is>
-          <t>SMD 0805</t>
+          <t>SMD 1206</t>
         </is>
       </c>
       <c r="F62" s="23" t="inlineStr">
@@ -2574,42 +2570,46 @@
         </is>
       </c>
       <c r="G62" s="23" t="n">
+        <v>6</v>
+      </c>
+      <c r="H62" s="24" t="inlineStr"/>
+    </row>
+    <row r="63" ht="20" customHeight="1">
+      <c r="A63" s="26" t="inlineStr">
+        <is>
+          <t>U7, U8, U9, U10, U11, U12, U13, U14</t>
+        </is>
+      </c>
+      <c r="B63" s="27" t="inlineStr">
+        <is>
+          <t>~</t>
+        </is>
+      </c>
+      <c r="C63" s="27" t="inlineStr">
+        <is>
+          <t>PC817</t>
+        </is>
+      </c>
+      <c r="D63" s="27" t="inlineStr"/>
+      <c r="E63" s="27" t="inlineStr">
+        <is>
+          <t>DIP-4 W7.62mm</t>
+        </is>
+      </c>
+      <c r="F63" s="27" t="inlineStr">
+        <is>
+          <t>Optocoupler</t>
+        </is>
+      </c>
+      <c r="G63" s="27" t="n">
         <v>8</v>
       </c>
-      <c r="H62" s="24" t="inlineStr"/>
-    </row>
-    <row r="63" ht="20" customHeight="1">
-      <c r="A63" s="25" t="inlineStr">
-        <is>
-          <t>R5, R9, R38, R44, R133, R137</t>
-        </is>
-      </c>
-      <c r="B63" s="23" t="inlineStr">
-        <is>
-          <t>8k</t>
-        </is>
-      </c>
-      <c r="C63" s="23" t="inlineStr"/>
-      <c r="D63" s="23" t="inlineStr"/>
-      <c r="E63" s="23" t="inlineStr">
-        <is>
-          <t>SMD 1206</t>
-        </is>
-      </c>
-      <c r="F63" s="23" t="inlineStr">
-        <is>
-          <t>Resistor SMD</t>
-        </is>
-      </c>
-      <c r="G63" s="23" t="n">
-        <v>6</v>
-      </c>
-      <c r="H63" s="24" t="inlineStr"/>
+      <c r="H63" s="28" t="inlineStr"/>
     </row>
     <row r="64" ht="20" customHeight="1">
-      <c r="A64" s="26" t="inlineStr">
-        <is>
-          <t>U7, U8, U9, U10, U11, U12, U13, U14</t>
+      <c r="A64" s="29" t="inlineStr">
+        <is>
+          <t>U5</t>
         </is>
       </c>
       <c r="B64" s="27" t="inlineStr">
@@ -2619,29 +2619,29 @@
       </c>
       <c r="C64" s="27" t="inlineStr">
         <is>
-          <t>PC817</t>
+          <t>APM32F405RGT6</t>
         </is>
       </c>
       <c r="D64" s="27" t="inlineStr"/>
       <c r="E64" s="27" t="inlineStr">
         <is>
-          <t>DIP-4 W7.62mm</t>
+          <t>LQFP-64 10x10mm P0.5mm</t>
         </is>
       </c>
       <c r="F64" s="27" t="inlineStr">
         <is>
-          <t>Optocoupler</t>
+          <t>MCU</t>
         </is>
       </c>
       <c r="G64" s="27" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="H64" s="28" t="inlineStr"/>
     </row>
     <row r="65" ht="20" customHeight="1">
       <c r="A65" s="29" t="inlineStr">
         <is>
-          <t>U5</t>
+          <t>U4, U31</t>
         </is>
       </c>
       <c r="B65" s="27" t="inlineStr">
@@ -2651,29 +2651,29 @@
       </c>
       <c r="C65" s="27" t="inlineStr">
         <is>
-          <t>APM32F405RGT6</t>
+          <t>TLV1117LV33DCYR</t>
         </is>
       </c>
       <c r="D65" s="27" t="inlineStr"/>
       <c r="E65" s="27" t="inlineStr">
         <is>
-          <t>LQFP-64 10x10mm P0.5mm</t>
+          <t>SOT-223-3</t>
         </is>
       </c>
       <c r="F65" s="27" t="inlineStr">
         <is>
-          <t>MCU</t>
+          <t>Linear regulator</t>
         </is>
       </c>
       <c r="G65" s="27" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H65" s="28" t="inlineStr"/>
     </row>
     <row r="66" ht="20" customHeight="1">
       <c r="A66" s="29" t="inlineStr">
         <is>
-          <t>U4, U31</t>
+          <t>U2, U3, U6, U17, U32, U33</t>
         </is>
       </c>
       <c r="B66" s="27" t="inlineStr">
@@ -2683,29 +2683,29 @@
       </c>
       <c r="C66" s="27" t="inlineStr">
         <is>
-          <t>TLV1117LV33DCYR</t>
+          <t>OPA333xxDBV</t>
         </is>
       </c>
       <c r="D66" s="27" t="inlineStr"/>
       <c r="E66" s="27" t="inlineStr">
         <is>
-          <t>SOT-223-3</t>
+          <t>SOT-23-5</t>
         </is>
       </c>
       <c r="F66" s="27" t="inlineStr">
         <is>
-          <t>Linear regulator</t>
+          <t>Op-Amp</t>
         </is>
       </c>
       <c r="G66" s="27" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="H66" s="28" t="inlineStr"/>
     </row>
     <row r="67" ht="20" customHeight="1">
       <c r="A67" s="29" t="inlineStr">
         <is>
-          <t>U2, U3, U6, U17, U32, U33</t>
+          <t>U16</t>
         </is>
       </c>
       <c r="B67" s="27" t="inlineStr">
@@ -2715,29 +2715,29 @@
       </c>
       <c r="C67" s="27" t="inlineStr">
         <is>
-          <t>OPA333xxDBV</t>
+          <t>USBLC6-2P6</t>
         </is>
       </c>
       <c r="D67" s="27" t="inlineStr"/>
       <c r="E67" s="27" t="inlineStr">
         <is>
-          <t>SOT-23-5</t>
+          <t>SOT-23-6</t>
         </is>
       </c>
       <c r="F67" s="27" t="inlineStr">
         <is>
-          <t>Op-Amp</t>
+          <t>ESD protection</t>
         </is>
       </c>
       <c r="G67" s="27" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="H67" s="28" t="inlineStr"/>
     </row>
     <row r="68" ht="20" customHeight="1">
       <c r="A68" s="29" t="inlineStr">
         <is>
-          <t>U16</t>
+          <t>U15</t>
         </is>
       </c>
       <c r="B68" s="27" t="inlineStr">
@@ -2747,18 +2747,18 @@
       </c>
       <c r="C68" s="27" t="inlineStr">
         <is>
-          <t>USBLC6-2P6</t>
+          <t>HT7550-1</t>
         </is>
       </c>
       <c r="D68" s="27" t="inlineStr"/>
       <c r="E68" s="27" t="inlineStr">
         <is>
-          <t>SOT-23-6</t>
+          <t>SOT-89-3</t>
         </is>
       </c>
       <c r="F68" s="27" t="inlineStr">
         <is>
-          <t>ESD protection</t>
+          <t>Linear regulator</t>
         </is>
       </c>
       <c r="G68" s="27" t="n">
@@ -2767,68 +2767,36 @@
       <c r="H68" s="28" t="inlineStr"/>
     </row>
     <row r="69" ht="20" customHeight="1">
-      <c r="A69" s="29" t="inlineStr">
-        <is>
-          <t>U15</t>
-        </is>
-      </c>
-      <c r="B69" s="27" t="inlineStr">
-        <is>
-          <t>~</t>
-        </is>
-      </c>
-      <c r="C69" s="27" t="inlineStr">
-        <is>
-          <t>HT7550-1</t>
-        </is>
-      </c>
-      <c r="D69" s="27" t="inlineStr"/>
-      <c r="E69" s="27" t="inlineStr">
-        <is>
-          <t>SOT-89-3</t>
-        </is>
-      </c>
-      <c r="F69" s="27" t="inlineStr">
-        <is>
-          <t>Linear regulator</t>
-        </is>
-      </c>
-      <c r="G69" s="27" t="n">
+      <c r="A69" s="30" t="inlineStr">
+        <is>
+          <t>Y1</t>
+        </is>
+      </c>
+      <c r="B69" s="31" t="inlineStr">
+        <is>
+          <t>16M</t>
+        </is>
+      </c>
+      <c r="C69" s="31" t="inlineStr">
+        <is>
+          <t>X322516MOB4SI</t>
+        </is>
+      </c>
+      <c r="D69" s="31" t="inlineStr"/>
+      <c r="E69" s="31" t="inlineStr">
+        <is>
+          <t>Crystal SMD SeikoEpson FA238-4Pin 3.2x2.5mm</t>
+        </is>
+      </c>
+      <c r="F69" s="31" t="inlineStr">
+        <is>
+          <t>Crystal</t>
+        </is>
+      </c>
+      <c r="G69" s="31" t="n">
         <v>1</v>
       </c>
-      <c r="H69" s="28" t="inlineStr"/>
-    </row>
-    <row r="70" ht="20" customHeight="1">
-      <c r="A70" s="30" t="inlineStr">
-        <is>
-          <t>Y1</t>
-        </is>
-      </c>
-      <c r="B70" s="31" t="inlineStr">
-        <is>
-          <t>16M</t>
-        </is>
-      </c>
-      <c r="C70" s="31" t="inlineStr">
-        <is>
-          <t>X322516MOB4SI</t>
-        </is>
-      </c>
-      <c r="D70" s="31" t="inlineStr"/>
-      <c r="E70" s="31" t="inlineStr">
-        <is>
-          <t>Crystal SMD SeikoEpson FA238-4Pin 3.2x2.5mm</t>
-        </is>
-      </c>
-      <c r="F70" s="31" t="inlineStr">
-        <is>
-          <t>Crystal</t>
-        </is>
-      </c>
-      <c r="G70" s="31" t="n">
-        <v>1</v>
-      </c>
-      <c r="H70" s="32" t="inlineStr"/>
+      <c r="H69" s="32" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
